--- a/assessment_forms/037_fire_safety_hazard_assessment--assessment_forms.xlsx
+++ b/assessment_forms/037_fire_safety_hazard_assessment--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -837,7 +837,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>fire_hazard_1</t>
+          <t>fire hazard 1</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>fire_hazard_2</t>
+          <t>fire hazard 2</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>fire_hazard_3</t>
+          <t>fire hazard 3</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>fire_hazard_4</t>
+          <t>fire hazard 4</t>
         </is>
       </c>
     </row>
@@ -905,7 +905,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>fire_hazard_5</t>
+          <t>fire hazard 5</t>
         </is>
       </c>
     </row>
@@ -922,7 +922,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>fire_hazard_1</t>
+          <t>fire hazard 1</t>
         </is>
       </c>
     </row>
@@ -939,7 +939,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>fire_hazard_2</t>
+          <t>fire hazard 2</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>fire_hazard_3</t>
+          <t>fire hazard 3</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>fire_hazard_4</t>
+          <t>fire hazard 4</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>fire_hazard_5</t>
+          <t>fire hazard 5</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>fire_hazard_1</t>
+          <t>fire hazard 1</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>fire_hazard_2</t>
+          <t>fire hazard 2</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>fire_hazard_3</t>
+          <t>fire hazard 3</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>fire_hazard_4</t>
+          <t>fire hazard 4</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>fire_hazard_5</t>
+          <t>fire hazard 5</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>fire_hazard_6</t>
+          <t>fire hazard 6</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>fire_hazard_7</t>
+          <t>fire hazard 7</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>fire_hazard_8</t>
+          <t>fire hazard 8</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>fire_hazard_9</t>
+          <t>fire hazard 9</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>fire_hazard_10</t>
+          <t>fire hazard 10</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>fire_hazard_11</t>
+          <t>fire hazard 11</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>fire_hazard_12</t>
+          <t>fire hazard 12</t>
         </is>
       </c>
     </row>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>fire_hazard_13</t>
+          <t>fire hazard 13</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>fire_hazard_14</t>
+          <t>fire hazard 14</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>fire_hazard_15</t>
+          <t>fire hazard 15</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>fire_hazard_16</t>
+          <t>fire hazard 16</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>fire_hazard_17</t>
+          <t>fire hazard 17</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>fire_hazard_18</t>
+          <t>fire hazard 18</t>
         </is>
       </c>
     </row>
